--- a/data/trans_orig/Q03B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q03B_R-Estudios-trans_orig.xlsx
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,44</t>
+          <t>1,18; 1,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,44</t>
+          <t>1,22; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,78</t>
+          <t>1,54; 1,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 3,96</t>
+          <t>3,68; 3,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 3,84</t>
+          <t>3,55; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 2,82</t>
+          <t>2,6; 2,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 2,74</t>
+          <t>2,53; 2,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,27</t>
+          <t>1,09; 1,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,56</t>
+          <t>1,41; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,73</t>
+          <t>1,6; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,7</t>
+          <t>3,46; 3,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 3,68</t>
+          <t>3,48; 3,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,44</t>
+          <t>2,27; 2,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,0</t>
+          <t>1,77; 2,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,89</t>
+          <t>2,58; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,19</t>
+          <t>2,84; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,26</t>
+          <t>2,92; 3,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,19</t>
+          <t>1,93; 2,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,2; 1,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,51</t>
+          <t>1,4; 1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,64</t>
+          <t>3,47; 3,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,58</t>
+          <t>3,44; 3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 3,53</t>
+          <t>3,39; 3,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 2,56</t>
+          <t>2,45; 2,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
